--- a/data/travel_sheet_v1_planning.xlsx
+++ b/data/travel_sheet_v1_planning.xlsx
@@ -429,14 +429,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -749,7 +747,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="11" width="16" customWidth="1"/>
-    <col min="12" max="12" width="41.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.3">
@@ -786,7 +784,7 @@
       <c r="K1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
